--- a/backtest_runs/20260410_193731/by_symbol/GHNI/GHNI.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/GHNI/GHNI.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1384.080000000003</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98615.92</v>
@@ -633,7 +633,7 @@
         <v>-3395.959999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>95412.68000000001</v>
@@ -679,7 +679,7 @@
         <v>-11091.62</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>84321.06</v>
@@ -771,7 +771,7 @@
         <v>-2312.639999999988</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>87746.22</v>
@@ -817,7 +817,7 @@
         <v>-3330.260000000008</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>84415.95999999999</v>
@@ -863,7 +863,7 @@
         <v>-610.2799999999927</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>83805.68000000001</v>
@@ -909,7 +909,7 @@
         <v>-2268.839999999995</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>81536.84000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-1484.819999999994</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>84705.03999999999</v>
@@ -1093,7 +1093,7 @@
         <v>-445.2999999999934</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>84259.74000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-8979</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>79917.70000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-1749.080000000003</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>78168.62</v>
@@ -1277,7 +1277,7 @@
         <v>-5609.319999999994</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>72559.30000000002</v>
@@ -1415,7 +1415,7 @@
         <v>-3448.52</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>74460.22</v>
@@ -1461,7 +1461,7 @@
         <v>-2553.540000000001</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>71906.68000000001</v>
